--- a/files/Mat.-Liste_GF_1.xlsx
+++ b/files/Mat.-Liste_GF_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS\P-IT\EPA\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099E5DD1-D815-4266-A73F-0506D17062DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA55F96-7758-4865-BDFE-02D8EAD0B548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -267,6 +267,12 @@
     <t>Sammler Wittenmoor    X</t>
   </si>
   <si>
+    <t xml:space="preserve">SM: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitarbeiter: </t>
+  </si>
+  <si>
     <t xml:space="preserve">Datum: </t>
   </si>
   <si>
@@ -274,12 +280,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ort/Str: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SM: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitarbeiter: </t>
   </si>
   <si>
     <t xml:space="preserve">NVt: </t>
@@ -1270,10 +1270,10 @@
       <c r="B1" s="44"/>
       <c r="C1" s="44"/>
       <c r="D1" s="45" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>72</v>
@@ -1287,13 +1287,13 @@
     </row>
     <row r="2" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="49" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B2" s="50"/>
       <c r="C2" s="50"/>
       <c r="D2" s="46"/>
       <c r="E2" s="51" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>78</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="3" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B3" s="50"/>
       <c r="C3" s="50"/>
@@ -1321,7 +1321,7 @@
     </row>
     <row r="4" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="49" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B4" s="50"/>
       <c r="C4" s="50"/>
